--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingRowsAndColumns.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingRowsAndColumns.xlsx
@@ -60,7 +60,14 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="1">
+  <x:fonts count="2">
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingRowsAndColumns.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingRowsAndColumns.xlsx
@@ -576,7 +576,7 @@
       <x:c r="A1" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
@@ -596,15 +596,6 @@
       <x:c r="B2" s="0" t="s"/>
       <x:c r="D2" s="0" t="s"/>
       <x:c r="F2" s="0" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:6">
-      <x:c r="B3" s="0" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:6">
-      <x:c r="B4" s="0" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:6">
-      <x:c r="B5" s="0" t="s"/>
     </x:row>
     <x:row r="6" spans="1:6">
       <x:c r="B6" s="0" t="s"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingRowsAndColumns.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CopyingRowsAndColumns.xlsx
@@ -104,22 +104,22 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="3">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="255" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
